--- a/artfynd/A 16581-2026 artfynd.xlsx
+++ b/artfynd/A 16581-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1250,6 +1250,113 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132542124</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97963</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Harsjön N, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>573462</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6618112</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lillhärad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16581-2026 artfynd.xlsx
+++ b/artfynd/A 16581-2026 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>132542124</v>
       </c>
       <c r="B7" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 16581-2026 artfynd.xlsx
+++ b/artfynd/A 16581-2026 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>132542124</v>
       </c>
       <c r="B7" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 16581-2026 artfynd.xlsx
+++ b/artfynd/A 16581-2026 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>132542124</v>
       </c>
       <c r="B7" t="n">
-        <v>97981</v>
+        <v>97982</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 16581-2026 artfynd.xlsx
+++ b/artfynd/A 16581-2026 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>132542124</v>
       </c>
       <c r="B7" t="n">
-        <v>97982</v>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 16581-2026 artfynd.xlsx
+++ b/artfynd/A 16581-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1358,6 +1358,663 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132803470</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Harsjön, Harsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>573614</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6618382</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lillhärad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gran/tallskog. Plantor på ca en kvm som växer vid en stig.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132804434</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Harsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>573822</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6618459</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lillhärad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Tjäderinventering Västmanland</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132804357</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Billsbo röse, Lillhärads sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>573806</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6618457</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lillhärad</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spillninghög på häll</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132804229</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Billsbo röse, Lillhärads sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>573802</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6618460</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lillhärad</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fjäder på häll</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Tjäderinventering Västmanland</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132806850</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Harsjön, Harsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>573722</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6618401</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lillhärad</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Plantor på ett område på ca 1 kvm.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16581-2026 artfynd.xlsx
+++ b/artfynd/A 16581-2026 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>132542124</v>
       </c>
       <c r="B7" t="n">
-        <v>97983</v>
+        <v>97984</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>132803470</v>
       </c>
       <c r="B8" t="n">
-        <v>106244</v>
+        <v>106245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>132804434</v>
       </c>
       <c r="B9" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>132804357</v>
       </c>
       <c r="B10" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>132804229</v>
       </c>
       <c r="B11" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>132806850</v>
       </c>
       <c r="B12" t="n">
-        <v>106244</v>
+        <v>106245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 16581-2026 artfynd.xlsx
+++ b/artfynd/A 16581-2026 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>132542124</v>
       </c>
       <c r="B7" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>132803470</v>
       </c>
       <c r="B8" t="n">
-        <v>106245</v>
+        <v>106247</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>132806850</v>
       </c>
       <c r="B12" t="n">
-        <v>106245</v>
+        <v>106247</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 16581-2026 artfynd.xlsx
+++ b/artfynd/A 16581-2026 artfynd.xlsx
@@ -1256,7 +1256,7 @@
         <v>132542124</v>
       </c>
       <c r="B7" t="n">
-        <v>97986</v>
+        <v>97987</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>132803470</v>
       </c>
       <c r="B8" t="n">
-        <v>106247</v>
+        <v>106248</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>132806850</v>
       </c>
       <c r="B12" t="n">
-        <v>106247</v>
+        <v>106248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 16581-2026 artfynd.xlsx
+++ b/artfynd/A 16581-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>114176186</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -793,15 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114257251</v>
+        <v>114257211</v>
       </c>
       <c r="B3" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,7 +818,6 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>äldre spillning</t>
@@ -841,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573852</v>
+        <v>573564</v>
       </c>
       <c r="R3" t="n">
-        <v>6618441</v>
+        <v>6618060</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -910,12 +899,7 @@
         <v>114257249</v>
       </c>
       <c r="B4" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,15 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114257211</v>
+        <v>114257251</v>
       </c>
       <c r="B5" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,6 +1035,7 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>äldre spillning</t>
@@ -1068,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573564</v>
+        <v>573852</v>
       </c>
       <c r="R5" t="n">
-        <v>6618060</v>
+        <v>6618441</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1137,12 +1117,7 @@
         <v>114257252</v>
       </c>
       <c r="B6" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132542124</v>
+        <v>132804229</v>
       </c>
       <c r="B7" t="n">
-        <v>97995</v>
+        <v>57162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,41 +1239,53 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Harsjön N, Vstm</t>
+          <t>Billsbo röse, Lillhärads sn, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573462</v>
+        <v>573802</v>
       </c>
       <c r="R7" t="n">
-        <v>6618112</v>
+        <v>6618460</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,12 +1309,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Fjäder på häll</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,34 +1338,37 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Tjäderinventering Västmanland</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132803470</v>
+        <v>132804254</v>
       </c>
       <c r="B8" t="n">
-        <v>106260</v>
+        <v>57162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,49 +1376,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Harsjön, Harsjön, Vstm</t>
+          <t>Billsbo röse, Lillhärads sn, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573614</v>
+        <v>573806</v>
       </c>
       <c r="R8" t="n">
-        <v>6618382</v>
+        <v>6618457</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,12 +1457,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gran/tallskog. Plantor på ca en kvm som växer vid en stig.</t>
+          <t>Spillningshög på häll</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,14 +1471,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1486,14 +1485,18 @@
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132806850</v>
+        <v>132804434</v>
       </c>
       <c r="B9" t="n">
-        <v>106260</v>
+        <v>57162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,53 +1504,49 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Harsjön, Harsjön, Vstm</t>
+          <t>Harsjön, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573722</v>
+        <v>573822</v>
       </c>
       <c r="R9" t="n">
-        <v>6618401</v>
+        <v>6618459</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1576,7 +1575,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1586,12 +1585,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Plantor på ett område på ca 1 kvm.</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,14 +1594,8 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1620,14 +1608,18 @@
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Tjäderinventering Västmanland</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132804434</v>
+        <v>132805151</v>
       </c>
       <c r="B10" t="n">
-        <v>57145</v>
+        <v>57162</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,14 +1659,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Harsjön, Vstm</t>
+          <t>Billsbo röse, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>573822</v>
+        <v>573826</v>
       </c>
       <c r="R10" t="n">
-        <v>6618459</v>
+        <v>6618637</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1706,7 +1698,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1716,7 +1708,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spillning på häll</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,6 +1724,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1747,10 +1749,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132804357</v>
+        <v>132803470</v>
       </c>
       <c r="B11" t="n">
-        <v>57145</v>
+        <v>106324</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,49 +1760,49 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Billsbo röse, Lillhärads sn, Vstm</t>
+          <t>Harsjön, Harsjön, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>573806</v>
+        <v>573614</v>
       </c>
       <c r="R11" t="n">
-        <v>6618457</v>
+        <v>6618382</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1829,7 +1831,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1839,12 +1841,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Spillninghög på häll</t>
+          <t>Gran/tallskog. Plantor på ca en kvm som växer vid en stig.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,12 +1855,13 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1872,18 +1875,14 @@
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Skogsprojektet</t>
-        </is>
-      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132804229</v>
+        <v>132806850</v>
       </c>
       <c r="B12" t="n">
-        <v>57145</v>
+        <v>106324</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1891,53 +1890,53 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Billsbo röse, Lillhärads sn, Vstm</t>
+          <t>Harsjön, Harsjön, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>573802</v>
+        <v>573722</v>
       </c>
       <c r="R12" t="n">
-        <v>6618460</v>
+        <v>6618401</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1966,7 +1965,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1976,12 +1975,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fjäder på häll</t>
+          <t>Plantor på ett område på ca 1 kvm.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1990,12 +1989,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2009,11 +2009,114 @@
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Tjäderinventering Västmanland</t>
-        </is>
-      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132542124</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Harsjön N, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>573462</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6618112</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lillhärad</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16581-2026 artfynd.xlsx
+++ b/artfynd/A 16581-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114176186</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257211</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257249</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257251</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257252</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1362,6 +1392,11 @@
           <t>Tjäderinventering Västmanland</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132804229</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1490,6 +1525,11 @@
           <t>Skogsprojektet</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132804254</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1613,6 +1653,11 @@
           <t>Tjäderinventering Västmanland</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132804434</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1746,6 +1791,11 @@
           <t>Tjäderinventering Västmanland</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132805151</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1876,6 +1926,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132803470</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2010,6 +2065,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132806850</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2117,8 +2177,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132542124</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>